--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -934,7 +934,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Assessment Date: 2026-07-09  |  Total Findings: 20  |  Stack: Node.js / Express / SQLite3</t>
+          <t>Assessment Date: 2026-07-22  |  Total Findings: 20  |  Stack: Node.js / Express / SQLite3</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tool: npm audit  |  Scan Date: 2026-07-09  |  Packages Analyzed: 10</t>
+          <t>Tool: npm audit  |  Scan Date: 2026-07-22  |  Packages Analyzed: 10</t>
         </is>
       </c>
     </row>
